--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_83_R9.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_83_R9.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.2044</v>
+        <v>4.0604</v>
       </c>
       <c r="E2" t="n">
-        <v>2.7933</v>
+        <v>2.75</v>
       </c>
       <c r="F2" t="n">
-        <v>1.4112</v>
+        <v>1.3104</v>
       </c>
       <c r="G2" t="n">
         <v>2.6351</v>
@@ -610,13 +610,13 @@
         <v>1.3917</v>
       </c>
       <c r="S2" t="n">
-        <v>1.7137</v>
+        <v>1.5696</v>
       </c>
       <c r="T2" t="n">
-        <v>1.2977</v>
+        <v>1.2544</v>
       </c>
       <c r="U2" t="n">
-        <v>0.416</v>
+        <v>0.3152</v>
       </c>
       <c r="V2" t="n">
         <v>-1.0722</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.0016</v>
+        <v>3.4955</v>
       </c>
       <c r="E3" t="n">
-        <v>1.7721</v>
+        <v>1.0644</v>
       </c>
       <c r="F3" t="n">
-        <v>2.2295</v>
+        <v>2.4311</v>
       </c>
       <c r="G3" t="n">
         <v>1.6733</v>
@@ -688,13 +688,13 @@
         <v>1.8556</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7046</v>
+        <v>0.1986</v>
       </c>
       <c r="T3" t="n">
-        <v>1.6711</v>
+        <v>0.9634</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.9665</v>
+        <v>-0.7648</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.3787</v>
+        <v>2.2689</v>
       </c>
       <c r="E4" t="n">
-        <v>1.6404</v>
+        <v>1.833</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7383999999999999</v>
+        <v>0.4359</v>
       </c>
       <c r="G4" t="n">
         <v>2.4317</v>
@@ -766,13 +766,13 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0.4626</v>
+        <v>0.3528</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2987</v>
+        <v>-0.1061</v>
       </c>
       <c r="U4" t="n">
-        <v>0.7613</v>
+        <v>0.4589</v>
       </c>
       <c r="V4" t="n">
         <v>-0.2836</v>
@@ -799,10 +799,10 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.0395</v>
+        <v>2.1141</v>
       </c>
       <c r="E5" t="n">
-        <v>1.0349</v>
+        <v>1.1096</v>
       </c>
       <c r="F5" t="n">
         <v>1.0046</v>
@@ -844,10 +844,10 @@
         <v>0.9278</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.7117</v>
+        <v>-0.637</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2987</v>
+        <v>-0.224</v>
       </c>
       <c r="U5" t="n">
         <v>-0.4129</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>C. MONEKE</t>
+          <t>N. KALINIC</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.8915</v>
+        <v>1.5209</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.3271</v>
+        <v>-1.271</v>
       </c>
       <c r="F6" t="n">
-        <v>2.2186</v>
+        <v>2.7919</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7742</v>
+        <v>1.6934</v>
       </c>
       <c r="H6" t="n">
-        <v>1.45</v>
+        <v>1.7636</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.6758</v>
+        <v>-0.0702</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7205</v>
+        <v>0.6641</v>
       </c>
       <c r="K6" t="n">
-        <v>0.9179</v>
+        <v>1.8822</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.1975</v>
+        <v>-1.2181</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0537</v>
+        <v>1.0293</v>
       </c>
       <c r="N6" t="n">
-        <v>0.5321</v>
+        <v>-0.1186</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.4783</v>
+        <v>1.1479</v>
       </c>
       <c r="P6" t="n">
-        <v>-2.5515</v>
+        <v>-1.3917</v>
       </c>
       <c r="Q6" t="n">
-        <v>-3.9432</v>
+        <v>-3.2473</v>
       </c>
       <c r="R6" t="n">
-        <v>1.3917</v>
+        <v>1.8556</v>
       </c>
       <c r="S6" t="n">
-        <v>1.5244</v>
+        <v>0.2888</v>
       </c>
       <c r="T6" t="n">
-        <v>0.7512</v>
+        <v>0.2401</v>
       </c>
       <c r="U6" t="n">
-        <v>0.7732</v>
+        <v>0.0488</v>
       </c>
       <c r="V6" t="n">
-        <v>2.1444</v>
+        <v>0.9304</v>
       </c>
       <c r="W6" t="n">
-        <v>2.1444</v>
+        <v>1.0722</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.0215</v>
+        <v>1.398</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.4354</v>
+        <v>-2.5967</v>
       </c>
       <c r="F7" t="n">
-        <v>3.4569</v>
+        <v>3.9946</v>
       </c>
       <c r="G7" t="n">
         <v>0.2168</v>
@@ -1000,13 +1000,13 @@
         <v>2.0876</v>
       </c>
       <c r="S7" t="n">
-        <v>0.9129</v>
+        <v>1.2893</v>
       </c>
       <c r="T7" t="n">
-        <v>1.1483</v>
+        <v>0.9871</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2355</v>
+        <v>0.3023</v>
       </c>
       <c r="V7" t="n">
         <v>0.8197</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>C. MILLER-MCINTYRE</t>
+          <t>C. MONEKE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4658</v>
+        <v>0.8387</v>
       </c>
       <c r="E8" t="n">
-        <v>-4.9076</v>
+        <v>-0.8421999999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>5.3734</v>
+        <v>1.6809</v>
       </c>
       <c r="G8" t="n">
-        <v>2.8371</v>
+        <v>0.7742</v>
       </c>
       <c r="H8" t="n">
-        <v>6.6215</v>
+        <v>1.45</v>
       </c>
       <c r="I8" t="n">
-        <v>-3.7844</v>
+        <v>-0.6758</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7712</v>
+        <v>0.7205</v>
       </c>
       <c r="K8" t="n">
-        <v>5.65</v>
+        <v>0.9179</v>
       </c>
       <c r="L8" t="n">
-        <v>-4.8787</v>
+        <v>-0.1975</v>
       </c>
       <c r="M8" t="n">
-        <v>2.0659</v>
+        <v>0.0537</v>
       </c>
       <c r="N8" t="n">
-        <v>0.9715</v>
+        <v>0.5321</v>
       </c>
       <c r="O8" t="n">
-        <v>1.0944</v>
+        <v>-0.4783</v>
       </c>
       <c r="P8" t="n">
+        <v>-2.5515</v>
+      </c>
+      <c r="Q8" t="n">
         <v>-3.9432</v>
       </c>
-      <c r="Q8" t="n">
-        <v>-6.4946</v>
-      </c>
       <c r="R8" t="n">
-        <v>2.5515</v>
+        <v>1.3917</v>
       </c>
       <c r="S8" t="n">
-        <v>0.894</v>
+        <v>0.4716</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1379</v>
+        <v>0.2361</v>
       </c>
       <c r="U8" t="n">
-        <v>0.7561</v>
+        <v>0.2355</v>
       </c>
       <c r="V8" t="n">
-        <v>0.6778999999999999</v>
+        <v>2.1444</v>
       </c>
       <c r="W8" t="n">
-        <v>0.6778999999999999</v>
+        <v>2.1444</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.273</v>
+        <v>0.7284</v>
       </c>
       <c r="E9" t="n">
-        <v>0.6203</v>
+        <v>1.2101</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.3473</v>
+        <v>-0.4817</v>
       </c>
       <c r="G9" t="n">
         <v>0.7038</v>
@@ -1156,13 +1156,13 @@
         <v>1.1598</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2864</v>
+        <v>0.1689</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4481</v>
+        <v>0.1417</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1617</v>
+        <v>0.0272</v>
       </c>
       <c r="V9" t="n">
         <v>-1.0722</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>N. KALINIC</t>
+          <t>C. MILLER-MCINTYRE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0424</v>
+        <v>0.347</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.0101</v>
+        <v>-4.5223</v>
       </c>
       <c r="F10" t="n">
-        <v>2.0525</v>
+        <v>4.8693</v>
       </c>
       <c r="G10" t="n">
-        <v>1.6934</v>
+        <v>2.8371</v>
       </c>
       <c r="H10" t="n">
-        <v>1.7636</v>
+        <v>6.6215</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.0702</v>
+        <v>-3.7844</v>
       </c>
       <c r="J10" t="n">
-        <v>0.6641</v>
+        <v>0.7712</v>
       </c>
       <c r="K10" t="n">
-        <v>1.8822</v>
+        <v>5.65</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.2181</v>
+        <v>-4.8787</v>
       </c>
       <c r="M10" t="n">
-        <v>1.0293</v>
+        <v>2.0659</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.1186</v>
+        <v>0.9715</v>
       </c>
       <c r="O10" t="n">
-        <v>1.1479</v>
+        <v>1.0944</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.3917</v>
+        <v>-3.9432</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.2473</v>
+        <v>-6.4946</v>
       </c>
       <c r="R10" t="n">
-        <v>1.8556</v>
+        <v>2.5515</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.1896</v>
+        <v>0.7752</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4991</v>
+        <v>0.5232</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.6906</v>
+        <v>0.252</v>
       </c>
       <c r="V10" t="n">
-        <v>0.9304</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="W10" t="n">
-        <v>1.0722</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.9906</v>
+        <v>-0.4852</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0564</v>
+        <v>0.5282</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.047</v>
+        <v>-1.0134</v>
       </c>
       <c r="G11" t="n">
         <v>0.2171</v>
@@ -1312,13 +1312,13 @@
         <v>0.6959</v>
       </c>
       <c r="S11" t="n">
-        <v>0.148</v>
+        <v>0.6535</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5228</v>
+        <v>-0.051</v>
       </c>
       <c r="U11" t="n">
-        <v>0.6708</v>
+        <v>0.7044</v>
       </c>
       <c r="V11" t="n">
         <v>-1.3558</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.663</v>
+        <v>-1.875</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.3502</v>
+        <v>-1.6294</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.3129</v>
+        <v>-0.2456</v>
       </c>
       <c r="G12" t="n">
         <v>-1.1851</v>
@@ -1390,13 +1390,13 @@
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>0.6818</v>
+        <v>0.4698</v>
       </c>
       <c r="T12" t="n">
-        <v>0.5623</v>
+        <v>0.2831</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1195</v>
+        <v>0.1867</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>13.6648</v>
+        <v>14.4117</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.113</v>
+        <v>-2.3663</v>
       </c>
       <c r="F13" t="n">
-        <v>16.7779</v>
+        <v>16.778</v>
       </c>
       <c r="G13" t="n">
         <v>10.9984</v>
@@ -1441,16 +1441,16 @@
         <v>-7.109899999999999</v>
       </c>
       <c r="J13" t="n">
-        <v>5.5652</v>
+        <v>5.565200000000002</v>
       </c>
       <c r="K13" t="n">
         <v>14.9849</v>
       </c>
       <c r="L13" t="n">
-        <v>-9.419800000000002</v>
+        <v>-9.4198</v>
       </c>
       <c r="M13" t="n">
-        <v>5.433200000000001</v>
+        <v>5.4332</v>
       </c>
       <c r="N13" t="n">
         <v>3.1233</v>
@@ -1459,7 +1459,7 @@
         <v>2.3101</v>
       </c>
       <c r="P13" t="n">
-        <v>-5.7989</v>
+        <v>-5.798899999999999</v>
       </c>
       <c r="Q13" t="n">
         <v>-19.7161</v>
@@ -1468,19 +1468,19 @@
         <v>13.9172</v>
       </c>
       <c r="S13" t="n">
-        <v>4.854299999999999</v>
+        <v>5.601100000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>3.5011</v>
+        <v>4.248</v>
       </c>
       <c r="U13" t="n">
-        <v>1.3531</v>
+        <v>1.3533</v>
       </c>
       <c r="V13" t="n">
         <v>3.6109</v>
       </c>
       <c r="W13" t="n">
-        <v>7.5365</v>
+        <v>7.536500000000001</v>
       </c>
       <c r="X13" t="n">
         <v>-3.9256</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.7786</v>
+        <v>2.8064</v>
       </c>
       <c r="E14" t="n">
-        <v>3.2661</v>
+        <v>1.9686</v>
       </c>
       <c r="F14" t="n">
-        <v>0.5125</v>
+        <v>0.8378</v>
       </c>
       <c r="G14" t="n">
         <v>1.5108</v>
@@ -1546,13 +1546,13 @@
         <v>2.5515</v>
       </c>
       <c r="S14" t="n">
-        <v>0.7885</v>
+        <v>-0.1836</v>
       </c>
       <c r="T14" t="n">
-        <v>1.172</v>
+        <v>-0.1254</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.3835</v>
+        <v>-0.0582</v>
       </c>
       <c r="V14" t="n">
         <v>-1.0722</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.1985</v>
+        <v>2.7204</v>
       </c>
       <c r="E15" t="n">
-        <v>0.3595</v>
+        <v>0.7133</v>
       </c>
       <c r="F15" t="n">
-        <v>1.839</v>
+        <v>2.0071</v>
       </c>
       <c r="G15" t="n">
         <v>0.6122</v>
@@ -1624,13 +1624,13 @@
         <v>1.6237</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.0373</v>
+        <v>0.4845</v>
       </c>
       <c r="T15" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.3618</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0452</v>
+        <v>0.1228</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.602</v>
+        <v>1.8043</v>
       </c>
       <c r="E16" t="n">
-        <v>1.1239</v>
+        <v>0.888</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4782</v>
+        <v>0.9164</v>
       </c>
       <c r="G16" t="n">
         <v>0.1937</v>
@@ -1702,13 +1702,13 @@
         <v>2.7834</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2333</v>
+        <v>0.4356</v>
       </c>
       <c r="T16" t="n">
-        <v>0.6335</v>
+        <v>0.3976</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.4002</v>
+        <v>0.038</v>
       </c>
       <c r="V16" t="n">
         <v>-1.6083</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. HERNANGOMEZ</t>
+          <t>K. SLOUKAS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4844</v>
+        <v>0.5604</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.587</v>
+        <v>0.3654</v>
       </c>
       <c r="F17" t="n">
-        <v>1.0714</v>
+        <v>0.195</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.0792</v>
+        <v>-5.0313</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.4272</v>
+        <v>-3.1105</v>
       </c>
       <c r="I17" t="n">
-        <v>0.348</v>
+        <v>-1.9208</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.2848</v>
+        <v>-3.304</v>
       </c>
       <c r="K17" t="n">
-        <v>0.6757</v>
+        <v>-1.1757</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.9604</v>
+        <v>-2.1283</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.7944</v>
+        <v>-1.7273</v>
       </c>
       <c r="N17" t="n">
-        <v>-2.1028</v>
+        <v>-1.9348</v>
       </c>
       <c r="O17" t="n">
-        <v>1.3084</v>
+        <v>0.2075</v>
       </c>
       <c r="P17" t="n">
-        <v>1.8556</v>
+        <v>2.5515</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>3.0154</v>
+        <v>2.5515</v>
       </c>
       <c r="S17" t="n">
-        <v>0.7802</v>
+        <v>0.7541</v>
       </c>
       <c r="T17" t="n">
-        <v>0.8575</v>
+        <v>0.311</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.07729999999999999</v>
+        <v>0.443</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.0722</v>
+        <v>2.2862</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>3.3584</v>
       </c>
       <c r="X17" t="n">
         <v>-1.0722</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>K. SLOUKAS</t>
+          <t>J. HERNANGOMEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2566</v>
+        <v>0.1978</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.1064</v>
+        <v>-0.9409</v>
       </c>
       <c r="F18" t="n">
-        <v>0.3631</v>
+        <v>1.1386</v>
       </c>
       <c r="G18" t="n">
-        <v>-5.0313</v>
+        <v>-1.0792</v>
       </c>
       <c r="H18" t="n">
-        <v>-3.1105</v>
+        <v>-1.4272</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.9208</v>
+        <v>0.348</v>
       </c>
       <c r="J18" t="n">
-        <v>-3.304</v>
+        <v>-0.2848</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.1757</v>
+        <v>0.6757</v>
       </c>
       <c r="L18" t="n">
-        <v>-2.1283</v>
+        <v>-0.9604</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.7273</v>
+        <v>-0.7944</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.9348</v>
+        <v>-2.1028</v>
       </c>
       <c r="O18" t="n">
-        <v>0.2075</v>
+        <v>1.3084</v>
       </c>
       <c r="P18" t="n">
-        <v>2.5515</v>
+        <v>1.8556</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R18" t="n">
-        <v>2.5515</v>
+        <v>3.0154</v>
       </c>
       <c r="S18" t="n">
-        <v>0.4503</v>
+        <v>0.4935</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1608</v>
+        <v>0.5036</v>
       </c>
       <c r="U18" t="n">
-        <v>0.6111</v>
+        <v>-0.0101</v>
       </c>
       <c r="V18" t="n">
-        <v>2.2862</v>
+        <v>-1.0722</v>
       </c>
       <c r="W18" t="n">
-        <v>3.3584</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
         <v>-1.0722</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.5898</v>
+        <v>-0.123</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.7368</v>
+        <v>-1.3829</v>
       </c>
       <c r="F19" t="n">
-        <v>1.147</v>
+        <v>1.2599</v>
       </c>
       <c r="G19" t="n">
         <v>0.4085</v>
@@ -1936,13 +1936,13 @@
         <v>0.9278</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.1606</v>
+        <v>-0.6939</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.6642</v>
+        <v>-0.3104</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.4964</v>
+        <v>-0.3835</v>
       </c>
       <c r="V19" t="n">
         <v>0.3943</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. GRIGONIS</t>
+          <t>K. MITOGLOU</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,58 +1969,58 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.9939</v>
+        <v>-0.4118</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.9736</v>
+        <v>-0.5865</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.0204</v>
+        <v>0.1747</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.9711</v>
+        <v>-0.8129</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1465</v>
+        <v>-1.6193</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.1176</v>
+        <v>0.8064</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.7495000000000001</v>
+        <v>-0.1582</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>-0.2318</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.7495000000000001</v>
+        <v>0.0736</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.2216</v>
+        <v>-0.6546999999999999</v>
       </c>
       <c r="N20" t="n">
-        <v>0.1465</v>
+        <v>-1.3875</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.368</v>
+        <v>0.7328</v>
       </c>
       <c r="P20" t="n">
-        <v>0.232</v>
+        <v>0.9278</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.232</v>
+        <v>0.9278</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2548</v>
+        <v>-0.5266999999999999</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.224</v>
+        <v>-0.4283</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0307</v>
+        <v>-0.0984</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>K. MITOGLOU</t>
+          <t>M. GRIGONIS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,58 +2047,58 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.1195</v>
+        <v>-1.0104</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.8224</v>
+        <v>-0.8556</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.2971</v>
+        <v>-0.1548</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.8129</v>
+        <v>-0.9711</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.6193</v>
+        <v>0.1465</v>
       </c>
       <c r="I21" t="n">
-        <v>0.8064</v>
+        <v>-1.1176</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.1582</v>
+        <v>-0.7495000000000001</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.2318</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0736</v>
+        <v>-0.7495000000000001</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.6546999999999999</v>
+        <v>-0.2216</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.3875</v>
+        <v>0.1465</v>
       </c>
       <c r="O21" t="n">
-        <v>0.7328</v>
+        <v>-0.368</v>
       </c>
       <c r="P21" t="n">
-        <v>0.9278</v>
+        <v>0.232</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.9278</v>
+        <v>0.232</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.2344</v>
+        <v>-0.2713</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6642</v>
+        <v>-0.1061</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.5702</v>
+        <v>-0.1652</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.9205</v>
+        <v>-1.6402</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.3277</v>
+        <v>-2.5636</v>
       </c>
       <c r="F22" t="n">
-        <v>0.4072</v>
+        <v>0.9234</v>
       </c>
       <c r="G22" t="n">
         <v>-1.9293</v>
@@ -2170,13 +2170,13 @@
         <v>1.3917</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.3829</v>
+        <v>-1.1026</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2513</v>
+        <v>-0.4872</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.1316</v>
+        <v>-0.6155</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.1421</v>
+        <v>-1.9905</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.1454</v>
+        <v>-2.0275</v>
       </c>
       <c r="F23" t="n">
-        <v>0.0033</v>
+        <v>0.0369</v>
       </c>
       <c r="G23" t="n">
         <v>-1.4845</v>
@@ -2248,13 +2248,13 @@
         <v>0.6959</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.1937</v>
+        <v>-0.0422</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.2161</v>
+        <v>-0.0982</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0224</v>
+        <v>0.056</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.9839</v>
+        <v>-4.3941</v>
       </c>
       <c r="E24" t="n">
-        <v>-5.0465</v>
+        <v>-4.9286</v>
       </c>
       <c r="F24" t="n">
-        <v>0.06270000000000001</v>
+        <v>0.5345</v>
       </c>
       <c r="G24" t="n">
         <v>-2.1182</v>
@@ -2326,13 +2326,13 @@
         <v>1.3917</v>
       </c>
       <c r="S24" t="n">
-        <v>-2.0796</v>
+        <v>-1.4899</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.1123</v>
+        <v>-0.9944</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.9673</v>
+        <v>-0.4955</v>
       </c>
       <c r="V24" t="n">
         <v>0.1418</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-10.2353</v>
+        <v>-9.824999999999999</v>
       </c>
       <c r="E25" t="n">
-        <v>-7.7815</v>
+        <v>-7.4277</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.4538</v>
+        <v>-2.3974</v>
       </c>
       <c r="G25" t="n">
         <v>-0.2972</v>
@@ -2404,13 +2404,13 @@
         <v>1.6237</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.7631</v>
+        <v>-0.3528</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.731</v>
+        <v>-0.3771</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.0321</v>
+        <v>0.0244</v>
       </c>
       <c r="V25" t="n">
         <v>-2.6805</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-13.6649</v>
+        <v>-11.3057</v>
       </c>
       <c r="E26" t="n">
-        <v>-16.7778</v>
+        <v>-16.778</v>
       </c>
       <c r="F26" t="n">
-        <v>3.1131</v>
+        <v>5.4721</v>
       </c>
       <c r="G26" t="n">
         <v>-10.9985</v>
@@ -2452,7 +2452,7 @@
         <v>-18.1082</v>
       </c>
       <c r="I26" t="n">
-        <v>7.1097</v>
+        <v>7.109700000000002</v>
       </c>
       <c r="J26" t="n">
         <v>-5.433199999999999</v>
@@ -2473,7 +2473,7 @@
         <v>9.4199</v>
       </c>
       <c r="P26" t="n">
-        <v>5.798899999999998</v>
+        <v>5.7989</v>
       </c>
       <c r="Q26" t="n">
         <v>-13.9172</v>
@@ -2482,13 +2482,13 @@
         <v>19.7161</v>
       </c>
       <c r="S26" t="n">
-        <v>-4.8541</v>
+        <v>-2.4953</v>
       </c>
       <c r="T26" t="n">
-        <v>-1.353</v>
+        <v>-1.3531</v>
       </c>
       <c r="U26" t="n">
-        <v>-3.500999999999999</v>
+        <v>-1.1422</v>
       </c>
       <c r="V26" t="n">
         <v>-3.6109</v>
